--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_medianeta_a_2018_metropolitana.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_medianeta_a_2018_metropolitana.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:50</t>
+    <t xml:space="preserve">2026-09-24 00:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -672,7 +672,7 @@
         <v>0.07</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0.16</v>
@@ -692,10 +692,10 @@
         <v>52</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0.22</v>
@@ -718,7 +718,7 @@
         <v>0.2</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.03</v>
@@ -738,13 +738,13 @@
         <v>52</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="12">
